--- a/gu_in/SkillForce.edf/Skill.xlsx
+++ b/gu_in/SkillForce.edf/Skill.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project RF X\Parser_Public_Releases\Parser_official\Database\gu_in\SkillForce.edf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{714D61AA-FC0C-4277-A745-DD191F0BECD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A835F869-7A86-4DE5-BE77-79BA57FA1C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1350,7 +1350,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="35">
+  <fills count="36">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1540,6 +1540,12 @@
         <fgColor indexed="43"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="13">
     <border>
@@ -1722,11 +1728,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -20747,4841 +20757,4841 @@
       </c>
       <c r="DT50" s="1"/>
     </row>
-    <row r="51" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+    <row r="51" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="4">
         <v>2</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51" s="4">
         <v>49</v>
       </c>
-      <c r="D51" s="2">
-        <v>0</v>
-      </c>
-      <c r="E51" s="2" t="s">
+      <c r="D51" s="4">
+        <v>0</v>
+      </c>
+      <c r="E51" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" s="4" t="s">
         <v>231</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="G51" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="H51" s="2" t="s">
+      <c r="H51" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="2">
-        <v>1</v>
-      </c>
-      <c r="K51" s="1">
-        <v>1</v>
-      </c>
-      <c r="L51" s="2" t="s">
+      <c r="I51" s="4">
+        <v>0</v>
+      </c>
+      <c r="J51" s="4">
+        <v>1</v>
+      </c>
+      <c r="K51" s="6">
+        <v>1</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="M51" s="2" t="s">
+      <c r="M51" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N51" s="2" t="s">
+      <c r="N51" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="O51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P51" s="2" t="s">
+      <c r="O51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P51" s="4" t="s">
         <v>233</v>
       </c>
-      <c r="Q51" s="2">
-        <v>0</v>
-      </c>
-      <c r="R51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T51" s="2">
-        <v>0</v>
-      </c>
-      <c r="U51" s="2">
-        <v>0</v>
-      </c>
-      <c r="V51" s="2">
+      <c r="Q51" s="4">
+        <v>0</v>
+      </c>
+      <c r="R51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T51" s="4">
+        <v>0</v>
+      </c>
+      <c r="U51" s="4">
+        <v>0</v>
+      </c>
+      <c r="V51" s="4">
         <v>120</v>
       </c>
-      <c r="W51" s="2" t="s">
+      <c r="W51" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y51" s="2" t="s">
+      <c r="X51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y51" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA51" s="2" t="s">
+      <c r="Z51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA51" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC51" s="2">
+      <c r="AB51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC51" s="4">
         <v>180000</v>
       </c>
-      <c r="AD51" s="2">
-        <v>1</v>
-      </c>
-      <c r="AE51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AF51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AG51" s="2" t="s">
+      <c r="AD51" s="4">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AF51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AG51" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="AH51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO51" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW51" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY51" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ51" s="2" t="s">
+      <c r="AH51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO51" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY51" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ51" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK51" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL51" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM51" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN51" s="2">
-        <v>1</v>
-      </c>
-      <c r="BO51" s="2">
+      <c r="BA51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ51" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL51" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM51" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN51" s="4">
+        <v>1</v>
+      </c>
+      <c r="BO51" s="4">
         <v>20</v>
       </c>
-      <c r="BP51" s="2">
-        <v>0</v>
-      </c>
-      <c r="BQ51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BR51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BS51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BT51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BU51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BV51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BW51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BX51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BY51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BZ51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CA51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CB51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CC51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CD51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CE51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CF51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF51" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG51" s="2">
+      <c r="BP51" s="4">
+        <v>0</v>
+      </c>
+      <c r="BQ51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BR51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BS51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BT51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BU51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BV51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BW51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BX51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BY51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BZ51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CA51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CB51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CC51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CD51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CE51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CF51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF51" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG51" s="4">
         <v>120</v>
       </c>
-      <c r="DH51" s="2">
+      <c r="DH51" s="4">
         <v>120</v>
       </c>
-      <c r="DI51" s="2">
+      <c r="DI51" s="4">
         <v>120</v>
       </c>
-      <c r="DJ51" s="2">
+      <c r="DJ51" s="4">
         <v>120</v>
       </c>
-      <c r="DK51" s="2">
+      <c r="DK51" s="4">
         <v>120</v>
       </c>
-      <c r="DL51" s="2">
+      <c r="DL51" s="4">
         <v>120</v>
       </c>
-      <c r="DM51" s="2">
+      <c r="DM51" s="4">
         <v>120</v>
       </c>
-      <c r="DN51" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO51" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP51" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ51" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR51" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS51" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT51" s="1"/>
+      <c r="DN51" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO51" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP51" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ51" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR51" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS51" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT51" s="6"/>
     </row>
-    <row r="52" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+    <row r="52" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="4">
         <v>4</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52" s="4">
         <v>56</v>
       </c>
-      <c r="D52" s="2">
-        <v>0</v>
-      </c>
-      <c r="E52" s="2" t="s">
+      <c r="D52" s="4">
+        <v>0</v>
+      </c>
+      <c r="E52" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="G52" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="H52" s="2" t="s">
+      <c r="H52" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="I52" s="2">
-        <v>0</v>
-      </c>
-      <c r="J52" s="2">
-        <v>1</v>
-      </c>
-      <c r="K52" s="1">
-        <v>1</v>
-      </c>
-      <c r="L52" s="2" t="s">
+      <c r="I52" s="4">
+        <v>0</v>
+      </c>
+      <c r="J52" s="4">
+        <v>1</v>
+      </c>
+      <c r="K52" s="6">
+        <v>1</v>
+      </c>
+      <c r="L52" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="M52" s="2" t="s">
+      <c r="M52" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N52" s="2" t="s">
+      <c r="N52" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P52" s="2" t="s">
+      <c r="O52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P52" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q52" s="2">
-        <v>0</v>
-      </c>
-      <c r="R52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T52" s="2">
-        <v>0</v>
-      </c>
-      <c r="U52" s="2">
-        <v>300</v>
-      </c>
-      <c r="V52" s="2">
-        <v>300</v>
-      </c>
-      <c r="W52" s="2" t="s">
+      <c r="Q52" s="4">
+        <v>0</v>
+      </c>
+      <c r="R52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T52" s="4">
+        <v>0</v>
+      </c>
+      <c r="U52" s="4">
+        <v>0</v>
+      </c>
+      <c r="V52" s="4">
+        <v>0</v>
+      </c>
+      <c r="W52" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y52" s="2" t="s">
+      <c r="X52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y52" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA52" s="2" t="s">
+      <c r="Z52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA52" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC52" s="2">
+      <c r="AB52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC52" s="4">
         <v>1000</v>
       </c>
-      <c r="AD52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG52" s="2" t="s">
+      <c r="AD52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG52" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO52" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW52" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX52" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY52" s="2">
+      <c r="AH52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO52" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW52" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX52" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY52" s="4">
         <v>180</v>
       </c>
-      <c r="AZ52" s="2" t="s">
+      <c r="AZ52" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="BA52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ52" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK52" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL52" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM52" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO52" s="2">
+      <c r="BA52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ52" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK52" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL52" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM52" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO52" s="4">
         <v>33</v>
       </c>
-      <c r="BP52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW52" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX52" s="2">
+      <c r="BP52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW52" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX52" s="4">
         <v>32</v>
       </c>
-      <c r="BY52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE52" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF52" s="2">
-        <v>1</v>
-      </c>
-      <c r="CG52" s="2">
+      <c r="BY52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE52" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF52" s="4">
+        <v>1</v>
+      </c>
+      <c r="CG52" s="4">
         <v>33</v>
       </c>
-      <c r="CH52" s="2">
+      <c r="CH52" s="4">
         <v>-200</v>
       </c>
-      <c r="CI52" s="2">
+      <c r="CI52" s="4">
         <v>-200</v>
       </c>
-      <c r="CJ52" s="2">
+      <c r="CJ52" s="4">
         <v>-200</v>
       </c>
-      <c r="CK52" s="2">
+      <c r="CK52" s="4">
         <v>-200</v>
       </c>
-      <c r="CL52" s="2">
+      <c r="CL52" s="4">
         <v>-200</v>
       </c>
-      <c r="CM52" s="2">
+      <c r="CM52" s="4">
         <v>-200</v>
       </c>
-      <c r="CN52" s="2">
+      <c r="CN52" s="4">
         <v>-200</v>
       </c>
-      <c r="CO52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF52" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG52" s="2">
+      <c r="CO52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF52" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG52" s="4">
         <v>1200</v>
       </c>
-      <c r="DH52" s="2">
+      <c r="DH52" s="4">
         <v>1200</v>
       </c>
-      <c r="DI52" s="2">
+      <c r="DI52" s="4">
         <v>1200</v>
       </c>
-      <c r="DJ52" s="2">
+      <c r="DJ52" s="4">
         <v>1200</v>
       </c>
-      <c r="DK52" s="2">
+      <c r="DK52" s="4">
         <v>1200</v>
       </c>
-      <c r="DL52" s="2">
+      <c r="DL52" s="4">
         <v>1200</v>
       </c>
-      <c r="DM52" s="2">
+      <c r="DM52" s="4">
         <v>1200</v>
       </c>
-      <c r="DN52" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR52" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS52" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT52" s="1"/>
+      <c r="DN52" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO52" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP52" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ52" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR52" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS52" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT52" s="6"/>
     </row>
-    <row r="53" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+    <row r="53" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="4">
         <v>4</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53" s="4">
         <v>56</v>
       </c>
-      <c r="D53" s="2">
-        <v>0</v>
-      </c>
-      <c r="E53" s="2" t="s">
+      <c r="D53" s="4">
+        <v>0</v>
+      </c>
+      <c r="E53" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="G53" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="H53" s="2" t="s">
+      <c r="H53" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="I53" s="2">
-        <v>0</v>
-      </c>
-      <c r="J53" s="2">
-        <v>1</v>
-      </c>
-      <c r="K53" s="1">
-        <v>1</v>
-      </c>
-      <c r="L53" s="2" t="s">
+      <c r="I53" s="4">
+        <v>0</v>
+      </c>
+      <c r="J53" s="4">
+        <v>1</v>
+      </c>
+      <c r="K53" s="6">
+        <v>1</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="M53" s="2" t="s">
+      <c r="M53" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N53" s="2" t="s">
+      <c r="N53" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="O53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P53" s="2" t="s">
+      <c r="O53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P53" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q53" s="2">
-        <v>0</v>
-      </c>
-      <c r="R53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T53" s="2">
-        <v>0</v>
-      </c>
-      <c r="U53" s="2">
-        <v>300</v>
-      </c>
-      <c r="V53" s="2">
-        <v>300</v>
-      </c>
-      <c r="W53" s="2" t="s">
+      <c r="Q53" s="4">
+        <v>0</v>
+      </c>
+      <c r="R53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T53" s="4">
+        <v>0</v>
+      </c>
+      <c r="U53" s="4">
+        <v>0</v>
+      </c>
+      <c r="V53" s="4">
+        <v>0</v>
+      </c>
+      <c r="W53" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y53" s="2" t="s">
+      <c r="X53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y53" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA53" s="2" t="s">
+      <c r="Z53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA53" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC53" s="2">
+      <c r="AB53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC53" s="4">
         <v>1000</v>
       </c>
-      <c r="AD53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG53" s="2" t="s">
+      <c r="AD53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG53" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO53" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW53" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY53" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ53" s="2" t="s">
+      <c r="AH53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO53" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW53" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY53" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ53" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ53" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK53" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL53" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM53" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO53" s="2">
+      <c r="BA53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ53" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK53" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL53" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM53" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO53" s="4">
         <v>33</v>
       </c>
-      <c r="BP53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW53" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX53" s="2">
+      <c r="BP53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW53" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX53" s="4">
         <v>32</v>
       </c>
-      <c r="BY53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE53" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF53" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG53" s="2">
+      <c r="BY53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE53" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF53" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG53" s="4">
         <v>10</v>
       </c>
-      <c r="DH53" s="2">
+      <c r="DH53" s="4">
         <v>10</v>
       </c>
-      <c r="DI53" s="2">
+      <c r="DI53" s="4">
         <v>10</v>
       </c>
-      <c r="DJ53" s="2">
+      <c r="DJ53" s="4">
         <v>10</v>
       </c>
-      <c r="DK53" s="2">
+      <c r="DK53" s="4">
         <v>10</v>
       </c>
-      <c r="DL53" s="2">
+      <c r="DL53" s="4">
         <v>10</v>
       </c>
-      <c r="DM53" s="2">
+      <c r="DM53" s="4">
         <v>10</v>
       </c>
-      <c r="DN53" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR53" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS53" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT53" s="1"/>
+      <c r="DN53" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO53" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP53" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ53" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR53" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS53" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT53" s="6"/>
     </row>
-    <row r="54" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+    <row r="54" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="4" t="s">
         <v>241</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="4">
         <v>4</v>
       </c>
-      <c r="C54" s="2">
+      <c r="C54" s="4">
         <v>57</v>
       </c>
-      <c r="D54" s="2">
-        <v>0</v>
-      </c>
-      <c r="E54" s="2" t="s">
+      <c r="D54" s="4">
+        <v>0</v>
+      </c>
+      <c r="E54" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="G54" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H54" s="2" t="s">
+      <c r="H54" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="I54" s="2">
-        <v>0</v>
-      </c>
-      <c r="J54" s="2">
-        <v>1</v>
-      </c>
-      <c r="K54" s="1">
-        <v>1</v>
-      </c>
-      <c r="L54" s="2" t="s">
+      <c r="I54" s="4">
+        <v>0</v>
+      </c>
+      <c r="J54" s="4">
+        <v>1</v>
+      </c>
+      <c r="K54" s="6">
+        <v>1</v>
+      </c>
+      <c r="L54" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="M54" s="2" t="s">
+      <c r="M54" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N54" s="2" t="s">
+      <c r="N54" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P54" s="2" t="s">
+      <c r="O54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P54" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q54" s="2">
-        <v>0</v>
-      </c>
-      <c r="R54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T54" s="2">
-        <v>0</v>
-      </c>
-      <c r="U54" s="2">
-        <v>300</v>
-      </c>
-      <c r="V54" s="2">
-        <v>300</v>
-      </c>
-      <c r="W54" s="2" t="s">
+      <c r="Q54" s="4">
+        <v>0</v>
+      </c>
+      <c r="R54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T54" s="4">
+        <v>0</v>
+      </c>
+      <c r="U54" s="4">
+        <v>0</v>
+      </c>
+      <c r="V54" s="4">
+        <v>0</v>
+      </c>
+      <c r="W54" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y54" s="2" t="s">
+      <c r="X54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y54" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA54" s="2" t="s">
+      <c r="Z54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA54" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC54" s="2">
+      <c r="AB54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC54" s="4">
         <v>1000</v>
       </c>
-      <c r="AD54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG54" s="2" t="s">
+      <c r="AD54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG54" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO54" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW54" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX54" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY54" s="2">
+      <c r="AH54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO54" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW54" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX54" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY54" s="4">
         <v>180</v>
       </c>
-      <c r="AZ54" s="2" t="s">
+      <c r="AZ54" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="BA54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ54" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK54" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL54" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM54" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO54" s="2">
+      <c r="BA54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ54" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK54" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL54" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM54" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO54" s="4">
         <v>9</v>
       </c>
-      <c r="BP54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW54" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX54" s="2">
+      <c r="BP54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW54" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX54" s="4">
         <v>32</v>
       </c>
-      <c r="BY54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE54" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF54" s="2">
-        <v>1</v>
-      </c>
-      <c r="CG54" s="2">
+      <c r="BY54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE54" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF54" s="4">
+        <v>1</v>
+      </c>
+      <c r="CG54" s="4">
         <v>33</v>
       </c>
-      <c r="CH54" s="2">
+      <c r="CH54" s="4">
         <v>-200</v>
       </c>
-      <c r="CI54" s="2">
+      <c r="CI54" s="4">
         <v>-200</v>
       </c>
-      <c r="CJ54" s="2">
+      <c r="CJ54" s="4">
         <v>-200</v>
       </c>
-      <c r="CK54" s="2">
+      <c r="CK54" s="4">
         <v>-200</v>
       </c>
-      <c r="CL54" s="2">
+      <c r="CL54" s="4">
         <v>-200</v>
       </c>
-      <c r="CM54" s="2">
+      <c r="CM54" s="4">
         <v>-200</v>
       </c>
-      <c r="CN54" s="2">
+      <c r="CN54" s="4">
         <v>-200</v>
       </c>
-      <c r="CO54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF54" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG54" s="2">
+      <c r="CO54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF54" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG54" s="4">
         <v>1200</v>
       </c>
-      <c r="DH54" s="2">
+      <c r="DH54" s="4">
         <v>1200</v>
       </c>
-      <c r="DI54" s="2">
+      <c r="DI54" s="4">
         <v>1200</v>
       </c>
-      <c r="DJ54" s="2">
+      <c r="DJ54" s="4">
         <v>1200</v>
       </c>
-      <c r="DK54" s="2">
+      <c r="DK54" s="4">
         <v>1200</v>
       </c>
-      <c r="DL54" s="2">
+      <c r="DL54" s="4">
         <v>1200</v>
       </c>
-      <c r="DM54" s="2">
+      <c r="DM54" s="4">
         <v>1200</v>
       </c>
-      <c r="DN54" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR54" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS54" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT54" s="1"/>
+      <c r="DN54" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR54" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS54" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT54" s="6"/>
     </row>
-    <row r="55" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+    <row r="55" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="4">
         <v>4</v>
       </c>
-      <c r="C55" s="2">
+      <c r="C55" s="4">
         <v>57</v>
       </c>
-      <c r="D55" s="2">
-        <v>0</v>
-      </c>
-      <c r="E55" s="2" t="s">
+      <c r="D55" s="4">
+        <v>0</v>
+      </c>
+      <c r="E55" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="G55" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="H55" s="2" t="s">
+      <c r="H55" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="I55" s="2">
-        <v>0</v>
-      </c>
-      <c r="J55" s="2">
-        <v>1</v>
-      </c>
-      <c r="K55" s="1">
-        <v>1</v>
-      </c>
-      <c r="L55" s="2" t="s">
+      <c r="I55" s="4">
+        <v>0</v>
+      </c>
+      <c r="J55" s="4">
+        <v>1</v>
+      </c>
+      <c r="K55" s="6">
+        <v>1</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="M55" s="2" t="s">
+      <c r="M55" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N55" s="2" t="s">
+      <c r="N55" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="O55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P55" s="2" t="s">
+      <c r="O55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P55" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q55" s="2">
-        <v>0</v>
-      </c>
-      <c r="R55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T55" s="2">
-        <v>0</v>
-      </c>
-      <c r="U55" s="2">
-        <v>300</v>
-      </c>
-      <c r="V55" s="2">
-        <v>300</v>
-      </c>
-      <c r="W55" s="2" t="s">
+      <c r="Q55" s="4">
+        <v>0</v>
+      </c>
+      <c r="R55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T55" s="4">
+        <v>0</v>
+      </c>
+      <c r="U55" s="4">
+        <v>0</v>
+      </c>
+      <c r="V55" s="4">
+        <v>0</v>
+      </c>
+      <c r="W55" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y55" s="2" t="s">
+      <c r="X55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y55" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA55" s="2" t="s">
+      <c r="Z55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA55" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC55" s="2">
+      <c r="AB55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC55" s="4">
         <v>1000</v>
       </c>
-      <c r="AD55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG55" s="2" t="s">
+      <c r="AD55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG55" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO55" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW55" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY55" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ55" s="2" t="s">
+      <c r="AH55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO55" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW55" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY55" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ55" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ55" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK55" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL55" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM55" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO55" s="2">
+      <c r="BA55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ55" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK55" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL55" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM55" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO55" s="4">
         <v>9</v>
       </c>
-      <c r="BP55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW55" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX55" s="2">
+      <c r="BP55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW55" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX55" s="4">
         <v>32</v>
       </c>
-      <c r="BY55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE55" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF55" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG55" s="2">
+      <c r="BY55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE55" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF55" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG55" s="4">
         <v>10</v>
       </c>
-      <c r="DH55" s="2">
+      <c r="DH55" s="4">
         <v>10</v>
       </c>
-      <c r="DI55" s="2">
+      <c r="DI55" s="4">
         <v>10</v>
       </c>
-      <c r="DJ55" s="2">
+      <c r="DJ55" s="4">
         <v>10</v>
       </c>
-      <c r="DK55" s="2">
+      <c r="DK55" s="4">
         <v>10</v>
       </c>
-      <c r="DL55" s="2">
+      <c r="DL55" s="4">
         <v>10</v>
       </c>
-      <c r="DM55" s="2">
+      <c r="DM55" s="4">
         <v>10</v>
       </c>
-      <c r="DN55" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR55" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS55" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT55" s="1"/>
+      <c r="DN55" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR55" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS55" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT55" s="6"/>
     </row>
-    <row r="56" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+    <row r="56" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="4">
         <v>4</v>
       </c>
-      <c r="C56" s="2">
+      <c r="C56" s="4">
         <v>56</v>
       </c>
-      <c r="D56" s="2">
-        <v>0</v>
-      </c>
-      <c r="E56" s="2" t="s">
+      <c r="D56" s="4">
+        <v>0</v>
+      </c>
+      <c r="E56" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F56" s="2" t="s">
+      <c r="F56" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="G56" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="H56" s="2" t="s">
+      <c r="H56" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="I56" s="2">
-        <v>0</v>
-      </c>
-      <c r="J56" s="2">
-        <v>1</v>
-      </c>
-      <c r="K56" s="1">
-        <v>1</v>
-      </c>
-      <c r="L56" s="2" t="s">
+      <c r="I56" s="4">
+        <v>0</v>
+      </c>
+      <c r="J56" s="4">
+        <v>1</v>
+      </c>
+      <c r="K56" s="6">
+        <v>1</v>
+      </c>
+      <c r="L56" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="M56" s="2" t="s">
+      <c r="M56" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N56" s="2" t="s">
+      <c r="N56" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P56" s="2" t="s">
+      <c r="O56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P56" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q56" s="2">
-        <v>0</v>
-      </c>
-      <c r="R56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T56" s="2">
-        <v>0</v>
-      </c>
-      <c r="U56" s="2">
-        <v>300</v>
-      </c>
-      <c r="V56" s="2">
-        <v>300</v>
-      </c>
-      <c r="W56" s="2" t="s">
+      <c r="Q56" s="4">
+        <v>0</v>
+      </c>
+      <c r="R56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T56" s="4">
+        <v>0</v>
+      </c>
+      <c r="U56" s="4">
+        <v>0</v>
+      </c>
+      <c r="V56" s="4">
+        <v>0</v>
+      </c>
+      <c r="W56" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y56" s="2" t="s">
+      <c r="X56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y56" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA56" s="2" t="s">
+      <c r="Z56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA56" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC56" s="2">
+      <c r="AB56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC56" s="4">
         <v>1000</v>
       </c>
-      <c r="AD56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG56" s="2" t="s">
+      <c r="AD56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG56" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO56" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW56" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX56" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY56" s="2">
+      <c r="AH56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO56" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW56" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX56" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY56" s="4">
         <v>180</v>
       </c>
-      <c r="AZ56" s="2" t="s">
+      <c r="AZ56" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="BA56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ56" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK56" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL56" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM56" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO56" s="2">
+      <c r="BA56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ56" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK56" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL56" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM56" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO56" s="4">
         <v>33</v>
       </c>
-      <c r="BP56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW56" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX56" s="2">
+      <c r="BP56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW56" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX56" s="4">
         <v>32</v>
       </c>
-      <c r="BY56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE56" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF56" s="2">
-        <v>1</v>
-      </c>
-      <c r="CG56" s="2">
+      <c r="BY56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE56" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF56" s="4">
+        <v>1</v>
+      </c>
+      <c r="CG56" s="4">
         <v>33</v>
       </c>
-      <c r="CH56" s="2">
+      <c r="CH56" s="4">
         <v>-200</v>
       </c>
-      <c r="CI56" s="2">
+      <c r="CI56" s="4">
         <v>-200</v>
       </c>
-      <c r="CJ56" s="2">
+      <c r="CJ56" s="4">
         <v>-200</v>
       </c>
-      <c r="CK56" s="2">
+      <c r="CK56" s="4">
         <v>-200</v>
       </c>
-      <c r="CL56" s="2">
+      <c r="CL56" s="4">
         <v>-200</v>
       </c>
-      <c r="CM56" s="2">
+      <c r="CM56" s="4">
         <v>-200</v>
       </c>
-      <c r="CN56" s="2">
+      <c r="CN56" s="4">
         <v>-200</v>
       </c>
-      <c r="CO56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF56" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG56" s="2">
+      <c r="CO56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF56" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG56" s="4">
         <v>1200</v>
       </c>
-      <c r="DH56" s="2">
+      <c r="DH56" s="4">
         <v>1200</v>
       </c>
-      <c r="DI56" s="2">
+      <c r="DI56" s="4">
         <v>1200</v>
       </c>
-      <c r="DJ56" s="2">
+      <c r="DJ56" s="4">
         <v>1200</v>
       </c>
-      <c r="DK56" s="2">
+      <c r="DK56" s="4">
         <v>1200</v>
       </c>
-      <c r="DL56" s="2">
+      <c r="DL56" s="4">
         <v>1200</v>
       </c>
-      <c r="DM56" s="2">
+      <c r="DM56" s="4">
         <v>1200</v>
       </c>
-      <c r="DN56" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR56" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS56" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT56" s="1"/>
+      <c r="DN56" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR56" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS56" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT56" s="6"/>
     </row>
-    <row r="57" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+    <row r="57" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="4">
         <v>4</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57" s="4">
         <v>56</v>
       </c>
-      <c r="D57" s="2">
-        <v>0</v>
-      </c>
-      <c r="E57" s="2" t="s">
+      <c r="D57" s="4">
+        <v>0</v>
+      </c>
+      <c r="E57" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F57" s="2" t="s">
+      <c r="F57" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="G57" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="H57" s="2" t="s">
+      <c r="H57" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="I57" s="2">
-        <v>0</v>
-      </c>
-      <c r="J57" s="2">
-        <v>1</v>
-      </c>
-      <c r="K57" s="1">
-        <v>1</v>
-      </c>
-      <c r="L57" s="2" t="s">
+      <c r="I57" s="4">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4">
+        <v>1</v>
+      </c>
+      <c r="K57" s="6">
+        <v>1</v>
+      </c>
+      <c r="L57" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="M57" s="2" t="s">
+      <c r="M57" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="N57" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="O57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P57" s="2" t="s">
+      <c r="O57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P57" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q57" s="2">
-        <v>0</v>
-      </c>
-      <c r="R57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T57" s="2">
-        <v>0</v>
-      </c>
-      <c r="U57" s="2">
-        <v>300</v>
-      </c>
-      <c r="V57" s="2">
-        <v>300</v>
-      </c>
-      <c r="W57" s="2" t="s">
+      <c r="Q57" s="4">
+        <v>0</v>
+      </c>
+      <c r="R57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T57" s="4">
+        <v>0</v>
+      </c>
+      <c r="U57" s="4">
+        <v>0</v>
+      </c>
+      <c r="V57" s="4">
+        <v>0</v>
+      </c>
+      <c r="W57" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y57" s="2" t="s">
+      <c r="X57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y57" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA57" s="2" t="s">
+      <c r="Z57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA57" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC57" s="2">
+      <c r="AB57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC57" s="4">
         <v>1000</v>
       </c>
-      <c r="AD57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG57" s="2" t="s">
+      <c r="AD57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG57" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO57" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW57" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY57" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ57" s="2" t="s">
+      <c r="AH57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO57" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW57" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY57" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ57" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ57" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK57" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL57" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM57" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO57" s="2">
+      <c r="BA57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ57" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK57" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL57" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM57" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO57" s="4">
         <v>33</v>
       </c>
-      <c r="BP57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW57" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX57" s="2">
+      <c r="BP57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW57" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX57" s="4">
         <v>32</v>
       </c>
-      <c r="BY57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE57" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF57" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG57" s="2">
+      <c r="BY57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE57" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF57" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG57" s="4">
         <v>10</v>
       </c>
-      <c r="DH57" s="2">
+      <c r="DH57" s="4">
         <v>10</v>
       </c>
-      <c r="DI57" s="2">
+      <c r="DI57" s="4">
         <v>10</v>
       </c>
-      <c r="DJ57" s="2">
+      <c r="DJ57" s="4">
         <v>10</v>
       </c>
-      <c r="DK57" s="2">
+      <c r="DK57" s="4">
         <v>10</v>
       </c>
-      <c r="DL57" s="2">
+      <c r="DL57" s="4">
         <v>10</v>
       </c>
-      <c r="DM57" s="2">
+      <c r="DM57" s="4">
         <v>10</v>
       </c>
-      <c r="DN57" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR57" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS57" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT57" s="1"/>
+      <c r="DN57" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR57" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS57" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT57" s="6"/>
     </row>
-    <row r="58" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+    <row r="58" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="4">
         <v>4</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58" s="4">
         <v>57</v>
       </c>
-      <c r="D58" s="2">
-        <v>0</v>
-      </c>
-      <c r="E58" s="2" t="s">
+      <c r="D58" s="4">
+        <v>0</v>
+      </c>
+      <c r="E58" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F58" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="G58" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="H58" s="2" t="s">
+      <c r="H58" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="I58" s="2">
-        <v>0</v>
-      </c>
-      <c r="J58" s="2">
-        <v>1</v>
-      </c>
-      <c r="K58" s="1">
-        <v>1</v>
-      </c>
-      <c r="L58" s="2" t="s">
+      <c r="I58" s="4">
+        <v>0</v>
+      </c>
+      <c r="J58" s="4">
+        <v>1</v>
+      </c>
+      <c r="K58" s="6">
+        <v>1</v>
+      </c>
+      <c r="L58" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="M58" s="2" t="s">
+      <c r="M58" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N58" s="2" t="s">
+      <c r="N58" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P58" s="2" t="s">
+      <c r="O58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P58" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q58" s="2">
-        <v>0</v>
-      </c>
-      <c r="R58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T58" s="2">
-        <v>0</v>
-      </c>
-      <c r="U58" s="2">
-        <v>300</v>
-      </c>
-      <c r="V58" s="2">
-        <v>300</v>
-      </c>
-      <c r="W58" s="2" t="s">
+      <c r="Q58" s="4">
+        <v>0</v>
+      </c>
+      <c r="R58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T58" s="4">
+        <v>0</v>
+      </c>
+      <c r="U58" s="4">
+        <v>0</v>
+      </c>
+      <c r="V58" s="4">
+        <v>0</v>
+      </c>
+      <c r="W58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y58" s="2" t="s">
+      <c r="X58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA58" s="2" t="s">
+      <c r="Z58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC58" s="2">
+      <c r="AB58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC58" s="4">
         <v>1000</v>
       </c>
-      <c r="AD58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG58" s="2" t="s">
+      <c r="AD58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG58" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO58" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW58" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX58" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY58" s="2">
+      <c r="AH58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO58" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW58" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX58" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY58" s="4">
         <v>180</v>
       </c>
-      <c r="AZ58" s="2" t="s">
+      <c r="AZ58" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="BA58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ58" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK58" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL58" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM58" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO58" s="2">
+      <c r="BA58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ58" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK58" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL58" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM58" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO58" s="4">
         <v>9</v>
       </c>
-      <c r="BP58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW58" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX58" s="2">
+      <c r="BP58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW58" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX58" s="4">
         <v>32</v>
       </c>
-      <c r="BY58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE58" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF58" s="2">
-        <v>1</v>
-      </c>
-      <c r="CG58" s="2">
+      <c r="BY58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE58" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF58" s="4">
+        <v>1</v>
+      </c>
+      <c r="CG58" s="4">
         <v>33</v>
       </c>
-      <c r="CH58" s="2">
+      <c r="CH58" s="4">
         <v>-200</v>
       </c>
-      <c r="CI58" s="2">
+      <c r="CI58" s="4">
         <v>-200</v>
       </c>
-      <c r="CJ58" s="2">
+      <c r="CJ58" s="4">
         <v>-200</v>
       </c>
-      <c r="CK58" s="2">
+      <c r="CK58" s="4">
         <v>-200</v>
       </c>
-      <c r="CL58" s="2">
+      <c r="CL58" s="4">
         <v>-200</v>
       </c>
-      <c r="CM58" s="2">
+      <c r="CM58" s="4">
         <v>-200</v>
       </c>
-      <c r="CN58" s="2">
+      <c r="CN58" s="4">
         <v>-200</v>
       </c>
-      <c r="CO58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF58" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG58" s="2">
+      <c r="CO58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF58" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG58" s="4">
         <v>1200</v>
       </c>
-      <c r="DH58" s="2">
+      <c r="DH58" s="4">
         <v>1200</v>
       </c>
-      <c r="DI58" s="2">
+      <c r="DI58" s="4">
         <v>1200</v>
       </c>
-      <c r="DJ58" s="2">
+      <c r="DJ58" s="4">
         <v>1200</v>
       </c>
-      <c r="DK58" s="2">
+      <c r="DK58" s="4">
         <v>1200</v>
       </c>
-      <c r="DL58" s="2">
+      <c r="DL58" s="4">
         <v>1200</v>
       </c>
-      <c r="DM58" s="2">
+      <c r="DM58" s="4">
         <v>1200</v>
       </c>
-      <c r="DN58" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO58" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP58" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ58" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR58" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS58" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT58" s="1"/>
+      <c r="DN58" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR58" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS58" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT58" s="6"/>
     </row>
-    <row r="59" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+    <row r="59" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="4">
         <v>4</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59" s="4">
         <v>57</v>
       </c>
-      <c r="D59" s="2">
-        <v>0</v>
-      </c>
-      <c r="E59" s="2" t="s">
+      <c r="D59" s="4">
+        <v>0</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F59" s="2" t="s">
+      <c r="F59" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G59" s="3" t="s">
+      <c r="G59" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="H59" s="2" t="s">
+      <c r="H59" s="4" t="s">
         <v>248</v>
       </c>
-      <c r="I59" s="2">
-        <v>0</v>
-      </c>
-      <c r="J59" s="2">
-        <v>1</v>
-      </c>
-      <c r="K59" s="1">
-        <v>1</v>
-      </c>
-      <c r="L59" s="2" t="s">
+      <c r="I59" s="4">
+        <v>0</v>
+      </c>
+      <c r="J59" s="4">
+        <v>1</v>
+      </c>
+      <c r="K59" s="6">
+        <v>1</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>362</v>
       </c>
-      <c r="M59" s="2" t="s">
+      <c r="M59" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="N59" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="O59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P59" s="2" t="s">
+      <c r="O59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P59" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q59" s="2">
-        <v>0</v>
-      </c>
-      <c r="R59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T59" s="2">
-        <v>0</v>
-      </c>
-      <c r="U59" s="2">
-        <v>300</v>
-      </c>
-      <c r="V59" s="2">
-        <v>300</v>
-      </c>
-      <c r="W59" s="2" t="s">
+      <c r="Q59" s="4">
+        <v>0</v>
+      </c>
+      <c r="R59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T59" s="4">
+        <v>0</v>
+      </c>
+      <c r="U59" s="4">
+        <v>0</v>
+      </c>
+      <c r="V59" s="4">
+        <v>0</v>
+      </c>
+      <c r="W59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y59" s="2" t="s">
+      <c r="X59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA59" s="2" t="s">
+      <c r="Z59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC59" s="2">
+      <c r="AB59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC59" s="4">
         <v>1000</v>
       </c>
-      <c r="AD59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG59" s="2" t="s">
+      <c r="AD59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO59" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW59" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY59" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ59" s="2" t="s">
+      <c r="AH59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO59" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW59" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY59" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ59" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK59" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL59" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM59" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO59" s="2">
+      <c r="BA59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ59" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK59" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL59" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM59" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO59" s="4">
         <v>9</v>
       </c>
-      <c r="BP59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW59" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX59" s="2">
+      <c r="BP59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW59" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX59" s="4">
         <v>32</v>
       </c>
-      <c r="BY59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE59" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF59" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG59" s="2">
+      <c r="BY59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE59" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF59" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG59" s="4">
         <v>10</v>
       </c>
-      <c r="DH59" s="2">
+      <c r="DH59" s="4">
         <v>10</v>
       </c>
-      <c r="DI59" s="2">
+      <c r="DI59" s="4">
         <v>10</v>
       </c>
-      <c r="DJ59" s="2">
+      <c r="DJ59" s="4">
         <v>10</v>
       </c>
-      <c r="DK59" s="2">
+      <c r="DK59" s="4">
         <v>10</v>
       </c>
-      <c r="DL59" s="2">
+      <c r="DL59" s="4">
         <v>10</v>
       </c>
-      <c r="DM59" s="2">
+      <c r="DM59" s="4">
         <v>10</v>
       </c>
-      <c r="DN59" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO59" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP59" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ59" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR59" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS59" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT59" s="1"/>
+      <c r="DN59" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR59" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS59" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT59" s="6"/>
     </row>
-    <row r="60" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+    <row r="60" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="4" t="s">
         <v>250</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="4">
         <v>4</v>
       </c>
-      <c r="C60" s="2">
+      <c r="C60" s="4">
         <v>56</v>
       </c>
-      <c r="D60" s="2">
-        <v>0</v>
-      </c>
-      <c r="E60" s="2" t="s">
+      <c r="D60" s="4">
+        <v>0</v>
+      </c>
+      <c r="E60" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F60" s="2" t="s">
+      <c r="F60" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="G60" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H60" s="2" t="s">
+      <c r="H60" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="I60" s="2">
-        <v>0</v>
-      </c>
-      <c r="J60" s="2">
-        <v>1</v>
-      </c>
-      <c r="K60" s="1">
-        <v>1</v>
-      </c>
-      <c r="L60" s="2" t="s">
+      <c r="I60" s="4">
+        <v>0</v>
+      </c>
+      <c r="J60" s="4">
+        <v>1</v>
+      </c>
+      <c r="K60" s="6">
+        <v>1</v>
+      </c>
+      <c r="L60" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="M60" s="2" t="s">
+      <c r="M60" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N60" s="2" t="s">
+      <c r="N60" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P60" s="2" t="s">
+      <c r="O60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P60" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q60" s="2">
-        <v>0</v>
-      </c>
-      <c r="R60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T60" s="2">
-        <v>0</v>
-      </c>
-      <c r="U60" s="2">
-        <v>300</v>
-      </c>
-      <c r="V60" s="2">
-        <v>300</v>
-      </c>
-      <c r="W60" s="2" t="s">
+      <c r="Q60" s="4">
+        <v>0</v>
+      </c>
+      <c r="R60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T60" s="4">
+        <v>0</v>
+      </c>
+      <c r="U60" s="4">
+        <v>0</v>
+      </c>
+      <c r="V60" s="4">
+        <v>0</v>
+      </c>
+      <c r="W60" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y60" s="2" t="s">
+      <c r="X60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y60" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA60" s="2" t="s">
+      <c r="Z60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA60" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC60" s="2">
+      <c r="AB60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC60" s="4">
         <v>1000</v>
       </c>
-      <c r="AD60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG60" s="2" t="s">
+      <c r="AD60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG60" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO60" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW60" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX60" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY60" s="2">
+      <c r="AH60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO60" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW60" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX60" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY60" s="4">
         <v>180</v>
       </c>
-      <c r="AZ60" s="2" t="s">
+      <c r="AZ60" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="BA60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ60" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK60" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL60" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM60" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO60" s="2">
+      <c r="BA60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ60" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK60" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL60" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM60" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO60" s="4">
         <v>33</v>
       </c>
-      <c r="BP60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW60" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX60" s="2">
+      <c r="BP60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW60" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX60" s="4">
         <v>32</v>
       </c>
-      <c r="BY60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE60" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF60" s="2">
-        <v>1</v>
-      </c>
-      <c r="CG60" s="2">
+      <c r="BY60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE60" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF60" s="4">
+        <v>1</v>
+      </c>
+      <c r="CG60" s="4">
         <v>33</v>
       </c>
-      <c r="CH60" s="2">
+      <c r="CH60" s="4">
         <v>-200</v>
       </c>
-      <c r="CI60" s="2">
+      <c r="CI60" s="4">
         <v>-200</v>
       </c>
-      <c r="CJ60" s="2">
+      <c r="CJ60" s="4">
         <v>-200</v>
       </c>
-      <c r="CK60" s="2">
+      <c r="CK60" s="4">
         <v>-200</v>
       </c>
-      <c r="CL60" s="2">
+      <c r="CL60" s="4">
         <v>-200</v>
       </c>
-      <c r="CM60" s="2">
+      <c r="CM60" s="4">
         <v>-200</v>
       </c>
-      <c r="CN60" s="2">
+      <c r="CN60" s="4">
         <v>-200</v>
       </c>
-      <c r="CO60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF60" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG60" s="2">
+      <c r="CO60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF60" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG60" s="4">
         <v>1200</v>
       </c>
-      <c r="DH60" s="2">
+      <c r="DH60" s="4">
         <v>1200</v>
       </c>
-      <c r="DI60" s="2">
+      <c r="DI60" s="4">
         <v>1200</v>
       </c>
-      <c r="DJ60" s="2">
+      <c r="DJ60" s="4">
         <v>1200</v>
       </c>
-      <c r="DK60" s="2">
+      <c r="DK60" s="4">
         <v>1200</v>
       </c>
-      <c r="DL60" s="2">
+      <c r="DL60" s="4">
         <v>1200</v>
       </c>
-      <c r="DM60" s="2">
+      <c r="DM60" s="4">
         <v>1200</v>
       </c>
-      <c r="DN60" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO60" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP60" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ60" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR60" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS60" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT60" s="1"/>
+      <c r="DN60" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR60" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS60" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT60" s="6"/>
     </row>
-    <row r="61" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+    <row r="61" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="4" t="s">
         <v>252</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="4">
         <v>4</v>
       </c>
-      <c r="C61" s="2">
+      <c r="C61" s="4">
         <v>56</v>
       </c>
-      <c r="D61" s="2">
-        <v>0</v>
-      </c>
-      <c r="E61" s="2" t="s">
+      <c r="D61" s="4">
+        <v>0</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F61" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="G61" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="H61" s="2" t="s">
+      <c r="H61" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="I61" s="2">
-        <v>0</v>
-      </c>
-      <c r="J61" s="2">
-        <v>1</v>
-      </c>
-      <c r="K61" s="1">
-        <v>1</v>
-      </c>
-      <c r="L61" s="2" t="s">
+      <c r="I61" s="4">
+        <v>0</v>
+      </c>
+      <c r="J61" s="4">
+        <v>1</v>
+      </c>
+      <c r="K61" s="6">
+        <v>1</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="M61" s="2" t="s">
+      <c r="M61" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N61" s="2" t="s">
+      <c r="N61" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="O61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P61" s="2" t="s">
+      <c r="O61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P61" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q61" s="2">
-        <v>0</v>
-      </c>
-      <c r="R61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T61" s="2">
-        <v>0</v>
-      </c>
-      <c r="U61" s="2">
-        <v>300</v>
-      </c>
-      <c r="V61" s="2">
-        <v>300</v>
-      </c>
-      <c r="W61" s="2" t="s">
+      <c r="Q61" s="4">
+        <v>0</v>
+      </c>
+      <c r="R61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T61" s="4">
+        <v>0</v>
+      </c>
+      <c r="U61" s="4">
+        <v>0</v>
+      </c>
+      <c r="V61" s="4">
+        <v>0</v>
+      </c>
+      <c r="W61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y61" s="2" t="s">
+      <c r="X61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA61" s="2" t="s">
+      <c r="Z61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC61" s="2">
+      <c r="AB61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC61" s="4">
         <v>1000</v>
       </c>
-      <c r="AD61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG61" s="2" t="s">
+      <c r="AD61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO61" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW61" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY61" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ61" s="2" t="s">
+      <c r="AH61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO61" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW61" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY61" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ61" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ61" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK61" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL61" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM61" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO61" s="2">
+      <c r="BA61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ61" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK61" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL61" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM61" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO61" s="4">
         <v>33</v>
       </c>
-      <c r="BP61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW61" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX61" s="2">
+      <c r="BP61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW61" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX61" s="4">
         <v>32</v>
       </c>
-      <c r="BY61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE61" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF61" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG61" s="2">
+      <c r="BY61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE61" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF61" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG61" s="4">
         <v>10</v>
       </c>
-      <c r="DH61" s="2">
+      <c r="DH61" s="4">
         <v>10</v>
       </c>
-      <c r="DI61" s="2">
+      <c r="DI61" s="4">
         <v>10</v>
       </c>
-      <c r="DJ61" s="2">
+      <c r="DJ61" s="4">
         <v>10</v>
       </c>
-      <c r="DK61" s="2">
+      <c r="DK61" s="4">
         <v>10</v>
       </c>
-      <c r="DL61" s="2">
+      <c r="DL61" s="4">
         <v>10</v>
       </c>
-      <c r="DM61" s="2">
+      <c r="DM61" s="4">
         <v>10</v>
       </c>
-      <c r="DN61" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO61" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP61" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ61" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR61" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS61" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT61" s="1"/>
+      <c r="DN61" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR61" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS61" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT61" s="6"/>
     </row>
-    <row r="62" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A62" s="2" t="s">
+    <row r="62" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="4">
         <v>4</v>
       </c>
-      <c r="C62" s="2">
+      <c r="C62" s="4">
         <v>57</v>
       </c>
-      <c r="D62" s="2">
-        <v>0</v>
-      </c>
-      <c r="E62" s="2" t="s">
+      <c r="D62" s="4">
+        <v>0</v>
+      </c>
+      <c r="E62" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F62" s="2" t="s">
+      <c r="F62" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="G62" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="H62" s="2" t="s">
+      <c r="H62" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="2">
-        <v>1</v>
-      </c>
-      <c r="K62" s="1">
-        <v>1</v>
-      </c>
-      <c r="L62" s="2" t="s">
+      <c r="I62" s="4">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4">
+        <v>1</v>
+      </c>
+      <c r="K62" s="6">
+        <v>1</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="M62" s="2" t="s">
+      <c r="M62" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="N62" s="2" t="s">
+      <c r="N62" s="4" t="s">
         <v>237</v>
       </c>
-      <c r="O62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P62" s="2" t="s">
+      <c r="O62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P62" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q62" s="2">
-        <v>0</v>
-      </c>
-      <c r="R62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T62" s="2">
-        <v>0</v>
-      </c>
-      <c r="U62" s="2">
-        <v>300</v>
-      </c>
-      <c r="V62" s="2">
-        <v>300</v>
-      </c>
-      <c r="W62" s="2" t="s">
+      <c r="Q62" s="4">
+        <v>0</v>
+      </c>
+      <c r="R62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T62" s="4">
+        <v>0</v>
+      </c>
+      <c r="U62" s="4">
+        <v>0</v>
+      </c>
+      <c r="V62" s="4">
+        <v>0</v>
+      </c>
+      <c r="W62" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y62" s="2" t="s">
+      <c r="X62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y62" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA62" s="2" t="s">
+      <c r="Z62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA62" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC62" s="2">
+      <c r="AB62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC62" s="4">
         <v>1000</v>
       </c>
-      <c r="AD62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG62" s="2" t="s">
+      <c r="AD62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG62" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO62" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW62" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX62" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY62" s="2">
+      <c r="AH62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO62" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW62" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX62" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY62" s="4">
         <v>180</v>
       </c>
-      <c r="AZ62" s="2" t="s">
+      <c r="AZ62" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="BA62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ62" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK62" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL62" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM62" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO62" s="2">
+      <c r="BA62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ62" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK62" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL62" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM62" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO62" s="4">
         <v>9</v>
       </c>
-      <c r="BP62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW62" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX62" s="2">
+      <c r="BP62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW62" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX62" s="4">
         <v>32</v>
       </c>
-      <c r="BY62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE62" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF62" s="2">
-        <v>1</v>
-      </c>
-      <c r="CG62" s="2">
+      <c r="BY62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE62" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF62" s="4">
+        <v>1</v>
+      </c>
+      <c r="CG62" s="4">
         <v>33</v>
       </c>
-      <c r="CH62" s="2">
+      <c r="CH62" s="4">
         <v>-200</v>
       </c>
-      <c r="CI62" s="2">
+      <c r="CI62" s="4">
         <v>-200</v>
       </c>
-      <c r="CJ62" s="2">
+      <c r="CJ62" s="4">
         <v>-200</v>
       </c>
-      <c r="CK62" s="2">
+      <c r="CK62" s="4">
         <v>-200</v>
       </c>
-      <c r="CL62" s="2">
+      <c r="CL62" s="4">
         <v>-200</v>
       </c>
-      <c r="CM62" s="2">
+      <c r="CM62" s="4">
         <v>-200</v>
       </c>
-      <c r="CN62" s="2">
+      <c r="CN62" s="4">
         <v>-200</v>
       </c>
-      <c r="CO62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF62" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG62" s="2">
+      <c r="CO62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF62" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG62" s="4">
         <v>1200</v>
       </c>
-      <c r="DH62" s="2">
+      <c r="DH62" s="4">
         <v>1200</v>
       </c>
-      <c r="DI62" s="2">
+      <c r="DI62" s="4">
         <v>1200</v>
       </c>
-      <c r="DJ62" s="2">
+      <c r="DJ62" s="4">
         <v>1200</v>
       </c>
-      <c r="DK62" s="2">
+      <c r="DK62" s="4">
         <v>1200</v>
       </c>
-      <c r="DL62" s="2">
+      <c r="DL62" s="4">
         <v>1200</v>
       </c>
-      <c r="DM62" s="2">
+      <c r="DM62" s="4">
         <v>1200</v>
       </c>
-      <c r="DN62" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO62" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP62" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ62" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR62" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS62" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT62" s="1"/>
+      <c r="DN62" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR62" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS62" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT62" s="6"/>
     </row>
-    <row r="63" spans="1:124" x14ac:dyDescent="0.25">
-      <c r="A63" s="2" t="s">
+    <row r="63" spans="1:124" s="7" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="4">
         <v>4</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C63" s="4">
         <v>57</v>
       </c>
-      <c r="D63" s="2">
-        <v>0</v>
-      </c>
-      <c r="E63" s="2" t="s">
+      <c r="D63" s="4">
+        <v>0</v>
+      </c>
+      <c r="E63" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="F63" s="2" t="s">
+      <c r="F63" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="G63" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="H63" s="2" t="s">
+      <c r="H63" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="I63" s="2">
-        <v>0</v>
-      </c>
-      <c r="J63" s="2">
-        <v>1</v>
-      </c>
-      <c r="K63" s="1">
-        <v>1</v>
-      </c>
-      <c r="L63" s="2" t="s">
+      <c r="I63" s="4">
+        <v>0</v>
+      </c>
+      <c r="J63" s="4">
+        <v>1</v>
+      </c>
+      <c r="K63" s="6">
+        <v>1</v>
+      </c>
+      <c r="L63" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="M63" s="2" t="s">
+      <c r="M63" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="N63" s="2" t="s">
+      <c r="N63" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="O63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="P63" s="2" t="s">
+      <c r="O63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="P63" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="Q63" s="2">
-        <v>0</v>
-      </c>
-      <c r="R63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="S63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="T63" s="2">
-        <v>0</v>
-      </c>
-      <c r="U63" s="2">
-        <v>300</v>
-      </c>
-      <c r="V63" s="2">
-        <v>300</v>
-      </c>
-      <c r="W63" s="2" t="s">
+      <c r="Q63" s="4">
+        <v>0</v>
+      </c>
+      <c r="R63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="S63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="T63" s="4">
+        <v>0</v>
+      </c>
+      <c r="U63" s="4">
+        <v>0</v>
+      </c>
+      <c r="V63" s="4">
+        <v>0</v>
+      </c>
+      <c r="W63" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="X63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="Y63" s="2" t="s">
+      <c r="X63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="Y63" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="Z63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AA63" s="2" t="s">
+      <c r="Z63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AA63" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AB63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AC63" s="2">
+      <c r="AB63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AC63" s="4">
         <v>1000</v>
       </c>
-      <c r="AD63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AE63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AF63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="AG63" s="2" t="s">
+      <c r="AD63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AE63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AF63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="AG63" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AH63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AI63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AJ63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AK63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AL63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AM63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AN63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AO63" s="2">
-        <v>8</v>
-      </c>
-      <c r="AP63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AQ63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AR63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AS63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AT63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AU63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AV63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AW63" s="1">
-        <v>-1</v>
-      </c>
-      <c r="AX63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AY63" s="2">
-        <v>0</v>
-      </c>
-      <c r="AZ63" s="2" t="s">
+      <c r="AH63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AI63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AJ63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AK63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AL63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AM63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AN63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AO63" s="4">
+        <v>8</v>
+      </c>
+      <c r="AP63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AQ63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AR63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AS63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AT63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AU63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AV63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AW63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="AX63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AY63" s="4">
+        <v>0</v>
+      </c>
+      <c r="AZ63" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="BA63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BB63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="BC63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BD63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BE63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BF63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BG63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BH63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BI63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BJ63" s="2">
-        <v>1</v>
-      </c>
-      <c r="BK63" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BL63" s="1">
-        <v>-1</v>
-      </c>
-      <c r="BM63" s="1">
-        <v>0</v>
-      </c>
-      <c r="BN63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BO63" s="2">
+      <c r="BA63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BB63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="BC63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BD63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BE63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BF63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BG63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BH63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BI63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BJ63" s="4">
+        <v>1</v>
+      </c>
+      <c r="BK63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BL63" s="6">
+        <v>-1</v>
+      </c>
+      <c r="BM63" s="6">
+        <v>0</v>
+      </c>
+      <c r="BN63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BO63" s="4">
         <v>9</v>
       </c>
-      <c r="BP63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BQ63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BR63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BS63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BT63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BU63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BV63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BW63" s="2">
-        <v>0</v>
-      </c>
-      <c r="BX63" s="2">
+      <c r="BP63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BQ63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BR63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BS63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BT63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BU63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BV63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BW63" s="4">
+        <v>0</v>
+      </c>
+      <c r="BX63" s="4">
         <v>32</v>
       </c>
-      <c r="BY63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="BZ63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CA63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CB63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CC63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CD63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CE63" s="2">
-        <v>0.20000000298023224</v>
-      </c>
-      <c r="CF63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CG63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CH63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CI63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CJ63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CK63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CL63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CM63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CN63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CO63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CP63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CQ63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CR63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CS63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CT63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CU63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CV63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CW63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CX63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CY63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="CZ63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DA63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DB63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DC63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DD63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DE63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DF63" s="2">
-        <v>-1</v>
-      </c>
-      <c r="DG63" s="2">
+      <c r="BY63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="BZ63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CA63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CB63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CC63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CD63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CE63" s="4">
+        <v>0.20000000298023224</v>
+      </c>
+      <c r="CF63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CG63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CH63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CI63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CJ63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CK63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CL63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CM63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CN63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CO63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CP63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CQ63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CR63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CS63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CT63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CU63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CV63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CW63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CX63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CY63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="CZ63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DA63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DB63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DC63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DD63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DE63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DF63" s="4">
+        <v>-1</v>
+      </c>
+      <c r="DG63" s="4">
         <v>10</v>
       </c>
-      <c r="DH63" s="2">
+      <c r="DH63" s="4">
         <v>10</v>
       </c>
-      <c r="DI63" s="2">
+      <c r="DI63" s="4">
         <v>10</v>
       </c>
-      <c r="DJ63" s="2">
+      <c r="DJ63" s="4">
         <v>10</v>
       </c>
-      <c r="DK63" s="2">
+      <c r="DK63" s="4">
         <v>10</v>
       </c>
-      <c r="DL63" s="2">
+      <c r="DL63" s="4">
         <v>10</v>
       </c>
-      <c r="DM63" s="2">
+      <c r="DM63" s="4">
         <v>10</v>
       </c>
-      <c r="DN63" s="1">
-        <v>0</v>
-      </c>
-      <c r="DO63" s="2">
-        <v>0</v>
-      </c>
-      <c r="DP63" s="2">
-        <v>0</v>
-      </c>
-      <c r="DQ63" s="2">
-        <v>0</v>
-      </c>
-      <c r="DR63" s="2">
-        <v>0</v>
-      </c>
-      <c r="DS63" s="2">
-        <v>1</v>
-      </c>
-      <c r="DT63" s="1"/>
+      <c r="DN63" s="6">
+        <v>0</v>
+      </c>
+      <c r="DO63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DP63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DQ63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DR63" s="4">
+        <v>0</v>
+      </c>
+      <c r="DS63" s="4">
+        <v>1</v>
+      </c>
+      <c r="DT63" s="6"/>
     </row>
     <row r="64" spans="1:124" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">

--- a/gu_in/SkillForce.edf/Skill.xlsx
+++ b/gu_in/SkillForce.edf/Skill.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project RF X\Parser_Public_Releases\Parser_official\Database\gu_in\SkillForce.edf\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A835F869-7A86-4DE5-BE77-79BA57FA1C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0826AC74-81A7-4518-BAC6-0A4FE68428C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
